--- a/entry_survey_cleaned.xlsx
+++ b/entry_survey_cleaned.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phamn\Documents\Project\Rebound Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5867FBDF-3E91-46FE-8D5E-80A3950CB8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45A28DC0-C3C1-4267-817F-6499D0ECDFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="4" xr2:uid="{1F6D650E-BEAC-4ADD-981F-43E816AAB90C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{1F6D650E-BEAC-4ADD-981F-43E816AAB90C}"/>
   </bookViews>
   <sheets>
     <sheet name="Expectation Theme" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1004" uniqueCount="222">
   <si>
     <t>Recorded Date</t>
   </si>
@@ -214,9 +214,6 @@
     <t>that it would be slower, revising over content and asking q</t>
   </si>
   <si>
-    <t>Practice</t>
-  </si>
-  <si>
     <t>it was decent, could ask q but thats it, really didnt have a structure imho</t>
   </si>
   <si>
@@ -503,12 +500,6 @@
     <t>Expectation Theme 5</t>
   </si>
   <si>
-    <t>Understand/Clarify Concepts</t>
-  </si>
-  <si>
-    <t>Assessments Help</t>
-  </si>
-  <si>
     <t>Theme</t>
   </si>
   <si>
@@ -659,6 +650,87 @@
   <si>
     <t>I want to join the Rebound program because I do not have any prior background or foundational knowledge in computer science or IT. As Iâ€šÃ„Ã´m beginning my studies in this field, I hope this course will help me build a solid foundation and strengthen my understanding so that I can keep up with the pace of my main program.
 In addition, I believe that many Others students who choose this course may come from similar non-technical backgrounds. I really look forward to learning and growing together with them, exchanging ideas, and supporting each Others throughout this journey.</t>
+  </si>
+  <si>
+    <t>Understand Concepts</t>
+  </si>
+  <si>
+    <t>No Comment</t>
+  </si>
+  <si>
+    <t>Unwell</t>
+  </si>
+  <si>
+    <t>To be more confident</t>
+  </si>
+  <si>
+    <t>Exams</t>
+  </si>
+  <si>
+    <t>Slower pace learning</t>
+  </si>
+  <si>
+    <t>Recap</t>
+  </si>
+  <si>
+    <t>Random</t>
+  </si>
+  <si>
+    <t>Late enrolment</t>
+  </si>
+  <si>
+    <t>Revise</t>
+  </si>
+  <si>
+    <t>New to IT</t>
+  </si>
+  <si>
+    <t>Receive Feedback</t>
+  </si>
+  <si>
+    <t>Theme 6</t>
+  </si>
+  <si>
+    <t>Theme 7</t>
+  </si>
+  <si>
+    <t>Theme 8</t>
+  </si>
+  <si>
+    <t>Theme 9</t>
+  </si>
+  <si>
+    <t>Expectation Theme  6</t>
+  </si>
+  <si>
+    <t>Expectation Theme 7</t>
+  </si>
+  <si>
+    <t>Expectation Theme 8</t>
+  </si>
+  <si>
+    <t>Expectation Theme 9</t>
+  </si>
+  <si>
+    <t>Expectation Theme 10</t>
+  </si>
+  <si>
+    <t>Expectation Theme 11</t>
+  </si>
+  <si>
+    <t>Expectation Theme 12</t>
+  </si>
+  <si>
+    <t>Expectation Theme 13</t>
+  </si>
+  <si>
+    <t>Expectation Theme 14</t>
+  </si>
+  <si>
+    <t>Expectation Theme 15</t>
+  </si>
+  <si>
+    <t>Missed lessons</t>
   </si>
 </sst>
 </file>
@@ -1045,18 +1117,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B9174D7-FE40-4E64-8EE3-13352E1607F3}">
-  <dimension ref="A1:Q73"/>
+  <dimension ref="A1:AA73"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.6328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.453125" customWidth="1"/>
     <col min="12" max="12" width="44.90625" customWidth="1"/>
     <col min="13" max="13" width="24.54296875" bestFit="1" customWidth="1"/>
     <col min="14" max="16" width="18.26953125" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="17.7265625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="18.36328125" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="18.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1094,22 +1170,52 @@
         <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="Q1" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R1" t="s">
+        <v>211</v>
+      </c>
+      <c r="S1" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="T1" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="U1" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="V1" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="W1" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="X1" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="Y1" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="Z1" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="AA1" s="4" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>45726.254166666666</v>
       </c>
@@ -1145,14 +1251,14 @@
         <v>14</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>45728.92291666667</v>
       </c>
@@ -1188,16 +1294,19 @@
         <v>16</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N3" s="1"/>
-      <c r="O3" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="P3" s="1"/>
+      <c r="O3" s="1"/>
+      <c r="P3" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="Q3" s="1"/>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="U3" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>45728.990277777775</v>
       </c>
@@ -1232,13 +1341,13 @@
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
+      <c r="O4" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="P4" s="1"/>
-      <c r="Q4" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="Q4" s="1"/>
+    </row>
+    <row r="5" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>45728.993750000001</v>
       </c>
@@ -1274,16 +1383,14 @@
         <v>18</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N5" s="1"/>
-      <c r="O5" s="1" t="s">
-        <v>192</v>
-      </c>
+      <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>45728.994444444441</v>
       </c>
@@ -1320,13 +1427,18 @@
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q6" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>45729.206944444442</v>
       </c>
@@ -1363,13 +1475,16 @@
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
       <c r="Q7" s="1"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Y7" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>45729.822222222225</v>
       </c>
@@ -1405,14 +1520,14 @@
         <v>25</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N8" s="1"/>
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>45729.82916666667</v>
       </c>
@@ -1448,14 +1563,17 @@
         <v>27</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N9" s="1"/>
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R9" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>45735.731944444444</v>
       </c>
@@ -1488,19 +1606,19 @@
         <v>4</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
       <c r="Q10" s="1"/>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>45735.990972222222</v>
       </c>
@@ -1535,15 +1653,15 @@
       <c r="L11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M11" s="1"/>
+      <c r="M11" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="N11" s="1"/>
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
-      <c r="Q11" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q11" s="1"/>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>45735.991666666669</v>
       </c>
@@ -1579,16 +1697,17 @@
         <v>33</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N12" s="1"/>
       <c r="O12" s="1"/>
-      <c r="P12" s="1" t="s">
-        <v>148</v>
-      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="S12" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>45735.991666666669</v>
       </c>
@@ -1624,14 +1743,14 @@
         <v>35</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N13" s="1"/>
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>45735.992361111108</v>
       </c>
@@ -1667,14 +1786,14 @@
         <v>37</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N14" s="1"/>
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>45735.993750000001</v>
       </c>
@@ -1710,14 +1829,14 @@
         <v>39</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N15" s="1"/>
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>45736.072222222225</v>
       </c>
@@ -1753,14 +1872,17 @@
         <v>41</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
       <c r="Q16" s="1"/>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Z16" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>45736.072222222225</v>
       </c>
@@ -1796,16 +1918,17 @@
         <v>43</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N17" s="1"/>
       <c r="O17" s="1"/>
-      <c r="P17" s="1" t="s">
-        <v>148</v>
-      </c>
+      <c r="P17" s="1"/>
       <c r="Q17" s="1"/>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="AA17" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>45736.073611111111</v>
       </c>
@@ -1840,15 +1963,18 @@
       <c r="L18" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="M18" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="M18" s="1"/>
       <c r="N18" s="1"/>
       <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
+      <c r="P18" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="Q18" s="1"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="T18" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>45736.073611111111</v>
       </c>
@@ -1884,14 +2010,14 @@
         <v>48</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N19" s="1"/>
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>45736.809027777781</v>
       </c>
@@ -1926,15 +2052,16 @@
       <c r="L20" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="M20" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="M20" s="1"/>
       <c r="N20" s="1"/>
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1"/>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="U20" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>45736.80972222222</v>
       </c>
@@ -1969,13 +2096,13 @@
       <c r="L21" s="1"/>
       <c r="M21" s="1"/>
       <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
+      <c r="O21" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="P21" s="1"/>
-      <c r="Q21" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q21" s="1"/>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>45736.80972222222</v>
       </c>
@@ -2012,13 +2139,13 @@
       </c>
       <c r="M22" s="1"/>
       <c r="N22" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
       <c r="Q22" s="1"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>45736.956250000003</v>
       </c>
@@ -2055,13 +2182,17 @@
       </c>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
-      <c r="O23" s="1" t="s">
-        <v>192</v>
-      </c>
+      <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1"/>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="T23" t="s">
+        <v>200</v>
+      </c>
+      <c r="X23" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>45742.991666666669</v>
       </c>
@@ -2094,17 +2225,17 @@
         <v>4</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>45742.991666666669</v>
       </c>
@@ -2137,19 +2268,20 @@
         <v>3</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N25" s="1"/>
-      <c r="O25" s="1" t="s">
-        <v>192</v>
-      </c>
+      <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1"/>
-    </row>
-    <row r="26" spans="1:17" ht="101.5" x14ac:dyDescent="0.35">
+      <c r="U25" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="101.5" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>45743.007638888892</v>
       </c>
@@ -2182,21 +2314,17 @@
         <v>4</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N26" s="1"/>
-      <c r="O26" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>148</v>
-      </c>
+      <c r="O26" s="1"/>
+      <c r="P26" s="1"/>
       <c r="Q26" s="1"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>45743.063194444447</v>
       </c>
@@ -2229,17 +2357,17 @@
         <v>3</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>45743.065972222219</v>
       </c>
@@ -2272,17 +2400,20 @@
         <v>2</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="Q28" s="1"/>
-    </row>
-    <row r="29" spans="1:17" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="S28" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>45743.065972222219</v>
       </c>
@@ -2315,21 +2446,19 @@
         <v>3</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>147</v>
-      </c>
+        <v>183</v>
+      </c>
+      <c r="M29" s="1"/>
       <c r="N29" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O29" s="1"/>
       <c r="P29" s="1" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>45743.822916666664</v>
       </c>
@@ -2362,17 +2491,18 @@
         <v>3</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
-      <c r="Q30" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q30" s="1"/>
+      <c r="V30" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>45743.823611111111</v>
       </c>
@@ -2389,35 +2519,35 @@
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2</v>
+      </c>
+      <c r="H31" s="1">
+        <v>2</v>
+      </c>
+      <c r="I31" s="1">
+        <v>4</v>
+      </c>
+      <c r="J31" s="1">
+        <v>4</v>
+      </c>
+      <c r="K31" s="1">
+        <v>4</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G31" s="1">
-        <v>2</v>
-      </c>
-      <c r="H31" s="1">
-        <v>2</v>
-      </c>
-      <c r="I31" s="1">
-        <v>4</v>
-      </c>
-      <c r="J31" s="1">
-        <v>4</v>
-      </c>
-      <c r="K31" s="1">
-        <v>4</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="M31" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>45743.82708333333</v>
       </c>
@@ -2450,17 +2580,17 @@
         <v>4</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1"/>
     </row>
-    <row r="33" spans="1:17" ht="29" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:27" ht="29" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>45743.82708333333</v>
       </c>
@@ -2493,19 +2623,19 @@
         <v>4</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
       <c r="Q33" s="1"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>45749.990972222222</v>
       </c>
@@ -2538,17 +2668,18 @@
         <v>3</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>147</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="M34" s="1"/>
       <c r="N34" s="1"/>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
       <c r="Q34" s="1"/>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="T34" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>45749.991666666669</v>
       </c>
@@ -2583,13 +2714,13 @@
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
       <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
+      <c r="O35" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="P35" s="1"/>
-      <c r="Q35" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q35" s="1"/>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>45749.99722222222</v>
       </c>
@@ -2622,17 +2753,17 @@
         <v>4</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
+      <c r="O36" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="P36" s="1"/>
-      <c r="Q36" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q36" s="1"/>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>45750.059027777781</v>
       </c>
@@ -2665,17 +2796,17 @@
         <v>4</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>45750.05972222222</v>
       </c>
@@ -2708,19 +2839,17 @@
         <v>2</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>184</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>45750.825694444444</v>
       </c>
@@ -2753,17 +2882,21 @@
         <v>4</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>147</v>
-      </c>
+        <v>82</v>
+      </c>
+      <c r="M39" s="1"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R39" t="s">
+        <v>198</v>
+      </c>
+      <c r="AA39" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>45757.050694444442</v>
       </c>
@@ -2796,17 +2929,20 @@
         <v>4</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1"/>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="X40" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>45757.859027777777</v>
       </c>
@@ -2839,17 +2975,18 @@
         <v>4</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M41" s="1"/>
-      <c r="N41" s="1" t="s">
-        <v>184</v>
-      </c>
+      <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1"/>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Y41" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>45757.861111111109</v>
       </c>
@@ -2882,17 +3019,17 @@
         <v>3</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M42" s="1"/>
       <c r="N42" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
       <c r="Q42" s="1"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>45785.037499999999</v>
       </c>
@@ -2925,17 +3062,20 @@
         <v>3</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
       <c r="Q43" s="1"/>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="S43" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>45785.866666666669</v>
       </c>
@@ -2968,17 +3108,17 @@
         <v>4</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>45785.867361111108</v>
       </c>
@@ -3011,17 +3151,18 @@
         <v>4</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>147</v>
-      </c>
+        <v>92</v>
+      </c>
+      <c r="M45" s="1"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1"/>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="U45" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>45792.827777777777</v>
       </c>
@@ -3054,17 +3195,23 @@
         <v>4</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M46" s="1"/>
-      <c r="N46" s="1" t="s">
-        <v>184</v>
-      </c>
+      <c r="N46" s="1"/>
       <c r="O46" s="1"/>
       <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q46" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="U46" t="s">
+        <v>201</v>
+      </c>
+      <c r="Y46" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>45799.111111111109</v>
       </c>
@@ -3097,19 +3244,20 @@
         <v>4</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="M47" s="1"/>
       <c r="N47" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O47" s="1"/>
-      <c r="P47" s="1" t="s">
-        <v>148</v>
-      </c>
+      <c r="P47" s="1"/>
       <c r="Q47" s="1"/>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="S47" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>45813.040972222225</v>
       </c>
@@ -3144,13 +3292,13 @@
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
+      <c r="O48" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="P48" s="1"/>
-      <c r="Q48" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q48" s="1"/>
+    </row>
+    <row r="49" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>45858.810416666667</v>
       </c>
@@ -3167,35 +3315,36 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G49" s="1">
+        <v>2</v>
+      </c>
+      <c r="H49" s="1">
+        <v>2</v>
+      </c>
+      <c r="I49" s="1">
+        <v>2</v>
+      </c>
+      <c r="J49" s="1">
+        <v>2</v>
+      </c>
+      <c r="K49" s="1">
+        <v>2</v>
+      </c>
+      <c r="L49" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="G49" s="1">
-        <v>2</v>
-      </c>
-      <c r="H49" s="1">
-        <v>2</v>
-      </c>
-      <c r="I49" s="1">
-        <v>2</v>
-      </c>
-      <c r="J49" s="1">
-        <v>2</v>
-      </c>
-      <c r="K49" s="1">
-        <v>2</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
-      <c r="O49" s="1" t="s">
-        <v>192</v>
-      </c>
+      <c r="O49" s="1"/>
       <c r="P49" s="1"/>
       <c r="Q49" s="1"/>
-    </row>
-    <row r="50" spans="1:17" ht="188.5" x14ac:dyDescent="0.35">
+      <c r="V49" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="50" spans="1:26" ht="188.5" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>45866.819444444445</v>
       </c>
@@ -3228,21 +3377,18 @@
         <v>4</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M50" s="1" t="s">
-        <v>147</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="M50" s="1"/>
       <c r="N50" s="1"/>
-      <c r="O50" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="P50" s="1" t="s">
-        <v>148</v>
-      </c>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
       <c r="Q50" s="1"/>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Z50" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="51" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>45867.022916666669</v>
       </c>
@@ -3259,7 +3405,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G51" s="1">
         <v>2</v>
@@ -3279,13 +3425,13 @@
       <c r="L51" s="1"/>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
+      <c r="O51" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="P51" s="1"/>
-      <c r="Q51" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q51" s="1"/>
+    </row>
+    <row r="52" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>45867.125694444447</v>
       </c>
@@ -3318,17 +3464,18 @@
         <v>3</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
-      <c r="O52" s="1" t="s">
-        <v>192</v>
-      </c>
+      <c r="O52" s="1"/>
       <c r="P52" s="1"/>
       <c r="Q52" s="1"/>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Z52" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="53" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>45875.166666666664</v>
       </c>
@@ -3361,17 +3508,17 @@
         <v>4</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
+      <c r="O53" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="P53" s="1"/>
-      <c r="Q53" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q53" s="1"/>
+    </row>
+    <row r="54" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>45876.782638888886</v>
       </c>
@@ -3404,17 +3551,17 @@
         <v>3</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
       <c r="P54" s="1"/>
       <c r="Q54" s="1"/>
     </row>
-    <row r="55" spans="1:17" ht="87" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:26" ht="87" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>45876.790277777778</v>
       </c>
@@ -3431,35 +3578,36 @@
         <v>1</v>
       </c>
       <c r="F55" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="G55" s="1">
+        <v>2</v>
+      </c>
+      <c r="H55" s="1">
+        <v>2</v>
+      </c>
+      <c r="I55" s="1">
+        <v>4</v>
+      </c>
+      <c r="J55" s="1">
+        <v>4</v>
+      </c>
+      <c r="K55" s="1">
+        <v>3</v>
+      </c>
+      <c r="L55" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="G55" s="1">
-        <v>2</v>
-      </c>
-      <c r="H55" s="1">
-        <v>2</v>
-      </c>
-      <c r="I55" s="1">
-        <v>4</v>
-      </c>
-      <c r="J55" s="1">
-        <v>4</v>
-      </c>
-      <c r="K55" s="1">
-        <v>3</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="M55" s="1" t="s">
-        <v>147</v>
-      </c>
+      <c r="M55" s="1"/>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
       <c r="P55" s="1"/>
       <c r="Q55" s="1"/>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="V55" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="56" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>45876.831250000003</v>
       </c>
@@ -3492,17 +3640,17 @@
         <v>4</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
       <c r="P56" s="1"/>
       <c r="Q56" s="1"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>45876.840277777781</v>
       </c>
@@ -3535,17 +3683,17 @@
         <v>3</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
       <c r="P57" s="1"/>
       <c r="Q57" s="1"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>45876.990972222222</v>
       </c>
@@ -3578,17 +3726,18 @@
         <v>4</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="M58" s="1" t="s">
-        <v>147</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="M58" s="1"/>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
       <c r="P58" s="1"/>
       <c r="Q58" s="1"/>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R58" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="59" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>45881.254861111112</v>
       </c>
@@ -3621,17 +3770,21 @@
         <v>4</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M59" s="1"/>
-      <c r="N59" s="1" t="s">
-        <v>184</v>
-      </c>
+      <c r="N59" s="1"/>
       <c r="O59" s="1"/>
       <c r="P59" s="1"/>
       <c r="Q59" s="1"/>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Y59" t="s">
+        <v>221</v>
+      </c>
+      <c r="Z59" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="60" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>45883.774305555555</v>
       </c>
@@ -3666,13 +3819,13 @@
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
+      <c r="O60" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="P60" s="1"/>
-      <c r="Q60" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="Q60" s="1"/>
+    </row>
+    <row r="61" spans="1:26" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>45883.77847222222</v>
       </c>
@@ -3705,17 +3858,17 @@
         <v>3</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
       <c r="P61" s="1"/>
       <c r="Q61" s="1"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>45883.870138888888</v>
       </c>
@@ -3748,17 +3901,17 @@
         <v>4</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
       <c r="P62" s="1"/>
       <c r="Q62" s="1"/>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>45883.870138888888</v>
       </c>
@@ -3791,17 +3944,20 @@
         <v>3</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="M63" s="1"/>
       <c r="N63" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="O63" s="1"/>
       <c r="P63" s="1"/>
       <c r="Q63" s="1"/>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Y63" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="64" spans="1:26" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>45883.911111111112</v>
       </c>
@@ -3834,17 +3990,20 @@
         <v>2</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="M64" s="1"/>
+        <v>123</v>
+      </c>
+      <c r="M64" s="1" t="s">
+        <v>195</v>
+      </c>
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
-      <c r="P64" s="1" t="s">
-        <v>148</v>
-      </c>
+      <c r="P64" s="1"/>
       <c r="Q64" s="1"/>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="S64" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>45890.861805555556</v>
       </c>
@@ -3879,13 +4038,13 @@
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
+      <c r="O65" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="P65" s="1"/>
-      <c r="Q65" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q65" s="1"/>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>45893.276388888888</v>
       </c>
@@ -3902,35 +4061,35 @@
         <v>1</v>
       </c>
       <c r="F66" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1</v>
+      </c>
+      <c r="I66" s="1">
+        <v>1</v>
+      </c>
+      <c r="J66" s="1">
+        <v>1</v>
+      </c>
+      <c r="K66" s="1">
+        <v>1</v>
+      </c>
+      <c r="L66" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="G66" s="1">
-        <v>1</v>
-      </c>
-      <c r="H66" s="1">
-        <v>1</v>
-      </c>
-      <c r="I66" s="1">
-        <v>1</v>
-      </c>
-      <c r="J66" s="1">
-        <v>1</v>
-      </c>
-      <c r="K66" s="1">
-        <v>1</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
+      <c r="O66" s="1" t="s">
+        <v>196</v>
+      </c>
       <c r="P66" s="1"/>
-      <c r="Q66" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q66" s="1"/>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>45896.156944444447</v>
       </c>
@@ -3963,17 +4122,17 @@
         <v>3</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M67" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
       <c r="P67" s="1"/>
       <c r="Q67" s="1"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>45896.156944444447</v>
       </c>
@@ -4006,17 +4165,18 @@
         <v>2</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="M68" s="1" t="s">
-        <v>147</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="M68" s="1"/>
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
       <c r="P68" s="1"/>
       <c r="Q68" s="1"/>
-    </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="V68" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>45896.157638888886</v>
       </c>
@@ -4049,19 +4209,17 @@
         <v>2</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="M69" s="1" t="s">
-        <v>147</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="M69" s="1"/>
       <c r="N69" s="1"/>
-      <c r="O69" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="P69" s="1"/>
+      <c r="O69" s="1"/>
+      <c r="P69" s="1" t="s">
+        <v>189</v>
+      </c>
       <c r="Q69" s="1"/>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>45897.854166666664</v>
       </c>
@@ -4094,17 +4252,17 @@
         <v>3</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M70" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
       <c r="P70" s="1"/>
       <c r="Q70" s="1"/>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>45904.861805555556</v>
       </c>
@@ -4121,7 +4279,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G71" s="1">
         <v>2</v>
@@ -4139,17 +4297,17 @@
         <v>4</v>
       </c>
       <c r="L71" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="M71" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="N71" s="1"/>
+        <v>188</v>
+      </c>
+      <c r="M71" s="1"/>
+      <c r="N71" s="1" t="s">
+        <v>181</v>
+      </c>
       <c r="O71" s="1"/>
       <c r="P71" s="1"/>
       <c r="Q71" s="1"/>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>45945.120138888888</v>
       </c>
@@ -4182,17 +4340,18 @@
         <v>4</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="M72" s="1" t="s">
-        <v>147</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="M72" s="1"/>
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
       <c r="P72" s="1"/>
       <c r="Q72" s="1"/>
-    </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="R72" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="73" spans="1:22" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>45945.12222222222</v>
       </c>
@@ -4225,10 +4384,10 @@
         <v>3</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M73" s="1" t="s">
-        <v>147</v>
+        <v>195</v>
       </c>
       <c r="N73" s="1"/>
       <c r="O73" s="1"/>
@@ -4236,16 +4395,21 @@
       <c r="Q73" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="C1:C73" xr:uid="{8B9174D7-FE40-4E64-8EE3-13352E1607F3}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A0F31FD4-A26D-4549-AE8D-1D09268F097C}">
           <x14:formula1>
             <xm:f>'Theme List'!$B$2:$F$2</xm:f>
           </x14:formula1>
-          <xm:sqref>M2:M73 N2:N1048576 O2:O1048576 P2:P1048576 Q2:Q1048576</xm:sqref>
+          <xm:sqref>N74:N1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{22642626-1114-4485-A32C-F29E0AD7862F}">
+          <x14:formula1>
+            <xm:f>'Theme List'!$B$2:$P$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>M2:M73 N2:N73 O2:O1048576 P2:P1048576 Q2:Q1048576 R2:AA73</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4305,19 +4469,19 @@
         <v>11</v>
       </c>
       <c r="M1" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>162</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
@@ -4360,7 +4524,7 @@
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
       <c r="Q2" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
@@ -4403,7 +4567,7 @@
       <c r="O3" s="1"/>
       <c r="P3" s="1"/>
       <c r="Q3" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
@@ -4444,7 +4608,7 @@
       <c r="O4" s="1"/>
       <c r="P4" s="1"/>
       <c r="Q4" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="130.5" x14ac:dyDescent="0.35">
@@ -4487,7 +4651,7 @@
       <c r="O5" s="1"/>
       <c r="P5" s="1"/>
       <c r="Q5" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
@@ -4527,13 +4691,13 @@
       </c>
       <c r="M6" s="1"/>
       <c r="N6" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q6" s="1"/>
     </row>
@@ -4574,7 +4738,7 @@
       </c>
       <c r="M7" s="1"/>
       <c r="N7" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O7" s="1"/>
       <c r="P7" s="1"/>
@@ -4620,7 +4784,7 @@
       <c r="O8" s="1"/>
       <c r="P8" s="1"/>
       <c r="Q8" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
@@ -4663,7 +4827,7 @@
       <c r="O9" s="1"/>
       <c r="P9" s="1"/>
       <c r="Q9" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
@@ -4703,7 +4867,7 @@
       </c>
       <c r="M10" s="1"/>
       <c r="N10" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
@@ -4749,7 +4913,7 @@
       <c r="O11" s="1"/>
       <c r="P11" s="1"/>
       <c r="Q11" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
@@ -4792,7 +4956,7 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
@@ -4835,7 +4999,7 @@
       <c r="O13" s="1"/>
       <c r="P13" s="1"/>
       <c r="Q13" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
@@ -4878,7 +5042,7 @@
       <c r="O14" s="1"/>
       <c r="P14" s="1"/>
       <c r="Q14" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
@@ -4921,7 +5085,7 @@
       <c r="O15" s="1"/>
       <c r="P15" s="1"/>
       <c r="Q15" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
@@ -4960,7 +5124,7 @@
         <v>41</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
@@ -5007,7 +5171,7 @@
       <c r="O17" s="1"/>
       <c r="P17" s="1"/>
       <c r="Q17" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
@@ -5047,7 +5211,7 @@
       </c>
       <c r="M18" s="1"/>
       <c r="N18" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O18" s="1"/>
       <c r="P18" s="1"/>
@@ -5093,7 +5257,7 @@
       <c r="O19" s="1"/>
       <c r="P19" s="1"/>
       <c r="Q19" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
@@ -5136,7 +5300,7 @@
       <c r="O20" s="1"/>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
@@ -5177,7 +5341,7 @@
       <c r="O21" s="1"/>
       <c r="P21" s="1"/>
       <c r="Q21" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
@@ -5217,7 +5381,7 @@
       </c>
       <c r="M22" s="1"/>
       <c r="N22" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O22" s="1"/>
       <c r="P22" s="1"/>
@@ -5263,7 +5427,7 @@
       <c r="O23" s="1"/>
       <c r="P23" s="1"/>
       <c r="Q23" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
@@ -5299,14 +5463,14 @@
         <v>4</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
       <c r="O24" s="1"/>
       <c r="P24" s="1"/>
       <c r="Q24" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
@@ -5342,14 +5506,14 @@
         <v>3</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="M25" s="1"/>
       <c r="N25" s="1"/>
       <c r="O25" s="1"/>
       <c r="P25" s="1"/>
       <c r="Q25" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="188.5" x14ac:dyDescent="0.35">
@@ -5385,14 +5549,14 @@
         <v>4</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
       <c r="O26" s="1"/>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
@@ -5428,14 +5592,14 @@
         <v>3</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="M27" s="1"/>
       <c r="N27" s="1"/>
       <c r="O27" s="1"/>
       <c r="P27" s="1"/>
       <c r="Q27" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
@@ -5471,14 +5635,14 @@
         <v>2</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="M28" s="1"/>
       <c r="N28" s="1"/>
       <c r="O28" s="1"/>
       <c r="P28" s="1"/>
       <c r="Q28" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="145" x14ac:dyDescent="0.35">
@@ -5514,15 +5678,15 @@
         <v>3</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="M29" s="1"/>
       <c r="N29" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O29" s="1"/>
       <c r="P29" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q29" s="1"/>
     </row>
@@ -5559,14 +5723,14 @@
         <v>3</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M30" s="1"/>
       <c r="N30" s="1"/>
       <c r="O30" s="1"/>
       <c r="P30" s="1"/>
       <c r="Q30" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
@@ -5586,32 +5750,32 @@
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="G31" s="1">
+        <v>2</v>
+      </c>
+      <c r="H31" s="1">
+        <v>2</v>
+      </c>
+      <c r="I31" s="1">
+        <v>4</v>
+      </c>
+      <c r="J31" s="1">
+        <v>4</v>
+      </c>
+      <c r="K31" s="1">
+        <v>4</v>
+      </c>
+      <c r="L31" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="G31" s="1">
-        <v>2</v>
-      </c>
-      <c r="H31" s="1">
-        <v>2</v>
-      </c>
-      <c r="I31" s="1">
-        <v>4</v>
-      </c>
-      <c r="J31" s="1">
-        <v>4</v>
-      </c>
-      <c r="K31" s="1">
-        <v>4</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>70</v>
       </c>
       <c r="M31" s="1"/>
       <c r="N31" s="1"/>
       <c r="O31" s="1"/>
       <c r="P31" s="1"/>
       <c r="Q31" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
@@ -5647,14 +5811,14 @@
         <v>4</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
       <c r="O32" s="1"/>
       <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:17" ht="87" x14ac:dyDescent="0.35">
@@ -5690,11 +5854,11 @@
         <v>4</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="M33" s="1"/>
       <c r="N33" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O33" s="1"/>
       <c r="P33" s="1"/>
@@ -5733,11 +5897,11 @@
         <v>3</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M34" s="1"/>
       <c r="N34" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O34" s="1"/>
       <c r="P34" s="1"/>
@@ -5781,7 +5945,7 @@
       <c r="O35" s="1"/>
       <c r="P35" s="1"/>
       <c r="Q35" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
@@ -5817,14 +5981,14 @@
         <v>4</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="M36" s="1"/>
       <c r="N36" s="1"/>
       <c r="O36" s="1"/>
       <c r="P36" s="1"/>
       <c r="Q36" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
@@ -5860,14 +6024,14 @@
         <v>4</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M37" s="1"/>
       <c r="N37" s="1"/>
       <c r="O37" s="1"/>
       <c r="P37" s="1"/>
       <c r="Q37" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
@@ -5903,14 +6067,14 @@
         <v>2</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
       <c r="P38" s="1"/>
       <c r="Q38" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
@@ -5946,12 +6110,12 @@
         <v>4</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1"/>
@@ -5989,14 +6153,14 @@
         <v>4</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M40" s="1"/>
       <c r="N40" s="1"/>
       <c r="O40" s="1"/>
       <c r="P40" s="1"/>
       <c r="Q40" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
@@ -6032,14 +6196,14 @@
         <v>4</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="M41" s="1"/>
       <c r="N41" s="1"/>
       <c r="O41" s="1"/>
       <c r="P41" s="1"/>
       <c r="Q41" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
@@ -6075,11 +6239,11 @@
         <v>3</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="M42" s="1"/>
       <c r="N42" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O42" s="1"/>
       <c r="P42" s="1"/>
@@ -6118,14 +6282,14 @@
         <v>3</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M43" s="1"/>
       <c r="N43" s="1"/>
       <c r="O43" s="1"/>
       <c r="P43" s="1"/>
       <c r="Q43" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
@@ -6161,14 +6325,14 @@
         <v>4</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="M44" s="1"/>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
       <c r="P44" s="1"/>
       <c r="Q44" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
@@ -6204,14 +6368,14 @@
         <v>4</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="M45" s="1"/>
       <c r="N45" s="1"/>
       <c r="O45" s="1"/>
       <c r="P45" s="1"/>
       <c r="Q45" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
@@ -6247,15 +6411,15 @@
         <v>4</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="M46" s="1"/>
       <c r="N46" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O46" s="1"/>
       <c r="P46" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q46" s="1"/>
     </row>
@@ -6292,11 +6456,11 @@
         <v>4</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M47" s="1"/>
       <c r="N47" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O47" s="1"/>
       <c r="P47" s="1"/>
@@ -6340,7 +6504,7 @@
       <c r="O48" s="1"/>
       <c r="P48" s="1"/>
       <c r="Q48" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
@@ -6360,31 +6524,31 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="G49" s="1">
+        <v>2</v>
+      </c>
+      <c r="H49" s="1">
+        <v>2</v>
+      </c>
+      <c r="I49" s="1">
+        <v>2</v>
+      </c>
+      <c r="J49" s="1">
+        <v>2</v>
+      </c>
+      <c r="K49" s="1">
+        <v>2</v>
+      </c>
+      <c r="L49" s="1" t="s">
         <v>99</v>
-      </c>
-      <c r="G49" s="1">
-        <v>2</v>
-      </c>
-      <c r="H49" s="1">
-        <v>2</v>
-      </c>
-      <c r="I49" s="1">
-        <v>2</v>
-      </c>
-      <c r="J49" s="1">
-        <v>2</v>
-      </c>
-      <c r="K49" s="1">
-        <v>2</v>
-      </c>
-      <c r="L49" s="1" t="s">
-        <v>100</v>
       </c>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
       <c r="P49" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q49" s="1"/>
     </row>
@@ -6421,10 +6585,10 @@
         <v>4</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
@@ -6448,7 +6612,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G51" s="1">
         <v>2</v>
@@ -6471,7 +6635,7 @@
       <c r="O51" s="1"/>
       <c r="P51" s="1"/>
       <c r="Q51" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
@@ -6507,10 +6671,10 @@
         <v>3</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
@@ -6550,14 +6714,14 @@
         <v>4</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
       <c r="P53" s="1"/>
       <c r="Q53" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
@@ -6593,14 +6757,14 @@
         <v>3</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
       <c r="P54" s="1"/>
       <c r="Q54" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="1:17" ht="174" x14ac:dyDescent="0.35">
@@ -6620,7 +6784,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G55" s="1">
         <v>2</v>
@@ -6638,13 +6802,13 @@
         <v>3</v>
       </c>
       <c r="L55" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
       <c r="P55" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q55" s="1"/>
     </row>
@@ -6681,14 +6845,14 @@
         <v>4</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
       <c r="P56" s="1"/>
       <c r="Q56" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
@@ -6724,14 +6888,14 @@
         <v>3</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
       <c r="P57" s="1"/>
       <c r="Q57" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
@@ -6767,14 +6931,14 @@
         <v>4</v>
       </c>
       <c r="L58" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
       <c r="P58" s="1"/>
       <c r="Q58" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
@@ -6810,13 +6974,13 @@
         <v>4</v>
       </c>
       <c r="L59" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N59" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O59" s="1"/>
       <c r="P59" s="1"/>
@@ -6860,7 +7024,7 @@
       <c r="O60" s="1"/>
       <c r="P60" s="1"/>
       <c r="Q60" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:17" ht="116" x14ac:dyDescent="0.35">
@@ -6896,14 +7060,14 @@
         <v>3</v>
       </c>
       <c r="L61" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
       <c r="P61" s="1"/>
       <c r="Q61" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
@@ -6939,14 +7103,14 @@
         <v>4</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
       <c r="P62" s="1"/>
       <c r="Q62" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
@@ -6982,15 +7146,15 @@
         <v>3</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="M63" s="1"/>
       <c r="N63" s="1" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="O63" s="1"/>
       <c r="P63" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="Q63" s="1"/>
     </row>
@@ -7027,14 +7191,14 @@
         <v>2</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
       <c r="P64" s="1"/>
       <c r="Q64" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="65" spans="1:17" x14ac:dyDescent="0.35">
@@ -7075,7 +7239,7 @@
       <c r="O65" s="1"/>
       <c r="P65" s="1"/>
       <c r="Q65" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
@@ -7095,32 +7259,32 @@
         <v>1</v>
       </c>
       <c r="F66" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1</v>
+      </c>
+      <c r="I66" s="1">
+        <v>1</v>
+      </c>
+      <c r="J66" s="1">
+        <v>1</v>
+      </c>
+      <c r="K66" s="1">
+        <v>1</v>
+      </c>
+      <c r="L66" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="G66" s="1">
-        <v>1</v>
-      </c>
-      <c r="H66" s="1">
-        <v>1</v>
-      </c>
-      <c r="I66" s="1">
-        <v>1</v>
-      </c>
-      <c r="J66" s="1">
-        <v>1</v>
-      </c>
-      <c r="K66" s="1">
-        <v>1</v>
-      </c>
-      <c r="L66" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
       <c r="P66" s="1"/>
       <c r="Q66" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
@@ -7156,14 +7320,14 @@
         <v>3</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
       <c r="P67" s="1"/>
       <c r="Q67" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
@@ -7199,14 +7363,14 @@
         <v>2</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M68" s="1"/>
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
       <c r="P68" s="1"/>
       <c r="Q68" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
@@ -7242,14 +7406,14 @@
         <v>2</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="M69" s="1"/>
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
       <c r="P69" s="1"/>
       <c r="Q69" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
@@ -7285,14 +7449,14 @@
         <v>3</v>
       </c>
       <c r="L70" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M70" s="1"/>
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
       <c r="P70" s="1"/>
       <c r="Q70" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
@@ -7312,32 +7476,32 @@
         <v>1</v>
       </c>
       <c r="F71" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G71" s="1">
+        <v>2</v>
+      </c>
+      <c r="H71" s="1">
+        <v>2</v>
+      </c>
+      <c r="I71" s="1">
+        <v>4</v>
+      </c>
+      <c r="J71" s="1">
+        <v>4</v>
+      </c>
+      <c r="K71" s="1">
+        <v>4</v>
+      </c>
+      <c r="L71" s="1" t="s">
         <v>136</v>
-      </c>
-      <c r="G71" s="1">
-        <v>2</v>
-      </c>
-      <c r="H71" s="1">
-        <v>2</v>
-      </c>
-      <c r="I71" s="1">
-        <v>4</v>
-      </c>
-      <c r="J71" s="1">
-        <v>4</v>
-      </c>
-      <c r="K71" s="1">
-        <v>4</v>
-      </c>
-      <c r="L71" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
       <c r="O71" s="1"/>
       <c r="P71" s="1"/>
       <c r="Q71" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.35">
@@ -7373,10 +7537,10 @@
         <v>4</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M72" s="1" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
@@ -7416,14 +7580,14 @@
         <v>3</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="M73" s="1"/>
       <c r="N73" s="1"/>
       <c r="O73" s="1"/>
       <c r="P73" s="1"/>
       <c r="Q73" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -7495,19 +7659,19 @@
         <v>12</v>
       </c>
       <c r="M1" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="P1" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>167</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="Q1" s="4" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
@@ -7545,7 +7709,7 @@
         <v>15</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
@@ -7583,7 +7747,7 @@
         <v>17</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
@@ -7618,7 +7782,7 @@
         <v>4</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
@@ -7656,7 +7820,7 @@
         <v>19</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
@@ -7694,7 +7858,7 @@
         <v>21</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
@@ -7732,7 +7896,7 @@
         <v>24</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
@@ -7770,7 +7934,7 @@
         <v>26</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
@@ -7808,10 +7972,10 @@
         <v>28</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
@@ -7849,7 +8013,7 @@
         <v>30</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P10" s="1" t="s">
         <v>47</v>
@@ -7890,7 +8054,7 @@
         <v>32</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
@@ -7928,7 +8092,7 @@
         <v>34</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
@@ -7966,7 +8130,7 @@
         <v>36</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
@@ -8004,7 +8168,7 @@
         <v>38</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>47</v>
@@ -8045,7 +8209,7 @@
         <v>40</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
@@ -8083,7 +8247,7 @@
         <v>42</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
@@ -8121,7 +8285,7 @@
         <v>44</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
@@ -8235,7 +8399,7 @@
         <v>51</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
@@ -8270,7 +8434,7 @@
         <v>4</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
@@ -8308,7 +8472,7 @@
         <v>53</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
@@ -8343,10 +8507,10 @@
         <v>1</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
@@ -8381,10 +8545,10 @@
         <v>4</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
@@ -8419,7 +8583,7 @@
         <v>3</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
@@ -8454,10 +8618,10 @@
         <v>4</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P26" s="1" t="s">
         <v>47</v>
@@ -8495,7 +8659,7 @@
         <v>3</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
@@ -8530,13 +8694,13 @@
         <v>2</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
@@ -8571,10 +8735,10 @@
         <v>3</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
@@ -8609,7 +8773,7 @@
         <v>3</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="P30" s="1" t="s">
         <v>47</v>
@@ -8632,7 +8796,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G31" s="1">
         <v>2</v>
@@ -8650,10 +8814,10 @@
         <v>4</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
@@ -8688,7 +8852,7 @@
         <v>4</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="P32" s="1" t="s">
         <v>47</v>
@@ -8726,10 +8890,10 @@
         <v>4</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
@@ -8764,7 +8928,7 @@
         <v>3</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
@@ -8799,7 +8963,7 @@
         <v>4</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
@@ -8834,10 +8998,10 @@
         <v>4</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
@@ -8872,10 +9036,10 @@
         <v>4</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
@@ -8910,7 +9074,7 @@
         <v>2</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="P38" s="1" t="s">
         <v>47</v>
@@ -8948,10 +9112,10 @@
         <v>4</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
@@ -8986,7 +9150,7 @@
         <v>4</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="P40" s="1" t="s">
         <v>47</v>
@@ -9024,7 +9188,7 @@
         <v>4</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
@@ -9059,10 +9223,10 @@
         <v>3</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P42" s="1" t="s">
         <v>47</v>
@@ -9100,7 +9264,7 @@
         <v>3</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
@@ -9135,10 +9299,10 @@
         <v>4</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
@@ -9173,10 +9337,10 @@
         <v>4</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P45" s="1" t="s">
         <v>47</v>
@@ -9214,10 +9378,10 @@
         <v>4</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
@@ -9252,13 +9416,13 @@
         <v>4</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
@@ -9293,7 +9457,7 @@
         <v>4</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:17" x14ac:dyDescent="0.35">
@@ -9313,7 +9477,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G49" s="1">
         <v>2</v>
@@ -9331,7 +9495,7 @@
         <v>2</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:17" x14ac:dyDescent="0.35">
@@ -9366,10 +9530,10 @@
         <v>4</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" spans="1:17" x14ac:dyDescent="0.35">
@@ -9389,7 +9553,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G51" s="1">
         <v>2</v>
@@ -9407,7 +9571,7 @@
         <v>2</v>
       </c>
       <c r="Q51" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:17" x14ac:dyDescent="0.35">
@@ -9442,7 +9606,7 @@
         <v>3</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P52" s="1" t="s">
         <v>47</v>
@@ -9480,10 +9644,10 @@
         <v>4</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" spans="1:17" x14ac:dyDescent="0.35">
@@ -9518,10 +9682,10 @@
         <v>3</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q54" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="1:17" x14ac:dyDescent="0.35">
@@ -9541,7 +9705,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G55" s="1">
         <v>2</v>
@@ -9559,10 +9723,10 @@
         <v>3</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="56" spans="1:17" x14ac:dyDescent="0.35">
@@ -9597,10 +9761,10 @@
         <v>4</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:17" x14ac:dyDescent="0.35">
@@ -9635,10 +9799,10 @@
         <v>3</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N57" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
@@ -9673,7 +9837,7 @@
         <v>4</v>
       </c>
       <c r="Q58" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
@@ -9708,7 +9872,7 @@
         <v>4</v>
       </c>
       <c r="Q59" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
@@ -9743,7 +9907,7 @@
         <v>4</v>
       </c>
       <c r="Q60" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
@@ -9778,10 +9942,10 @@
         <v>3</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="M61" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
@@ -9816,10 +9980,10 @@
         <v>4</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="N62" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P62" s="1" t="s">
         <v>47</v>
@@ -9857,7 +10021,7 @@
         <v>3</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="P63" s="1" t="s">
         <v>47</v>
@@ -9895,7 +10059,7 @@
         <v>2</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P64" s="1" t="s">
         <v>47</v>
@@ -9933,7 +10097,7 @@
         <v>4</v>
       </c>
       <c r="Q65" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="1:17" x14ac:dyDescent="0.35">
@@ -9953,7 +10117,7 @@
         <v>1</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -9971,10 +10135,10 @@
         <v>1</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="Q66" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:17" x14ac:dyDescent="0.35">
@@ -10009,10 +10173,10 @@
         <v>3</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="Q67" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:17" x14ac:dyDescent="0.35">
@@ -10047,10 +10211,10 @@
         <v>2</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="Q68" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" spans="1:17" x14ac:dyDescent="0.35">
@@ -10085,10 +10249,10 @@
         <v>2</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
     <row r="70" spans="1:17" x14ac:dyDescent="0.35">
@@ -10123,7 +10287,7 @@
         <v>3</v>
       </c>
       <c r="Q70" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="71" spans="1:17" x14ac:dyDescent="0.35">
@@ -10143,7 +10307,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G71" s="1">
         <v>2</v>
@@ -10161,7 +10325,7 @@
         <v>4</v>
       </c>
       <c r="Q71" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="72" spans="1:17" x14ac:dyDescent="0.35">
@@ -10196,10 +10360,10 @@
         <v>4</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="Q72" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" spans="1:17" x14ac:dyDescent="0.35">
@@ -10234,10 +10398,10 @@
         <v>3</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
     </row>
   </sheetData>
@@ -10307,16 +10471,16 @@
         <v>12</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="P1" s="1" t="s">
         <v>177</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>178</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
@@ -10354,7 +10518,7 @@
         <v>15</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
@@ -10392,7 +10556,7 @@
         <v>17</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
@@ -10427,7 +10591,7 @@
         <v>4</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
@@ -10465,7 +10629,7 @@
         <v>19</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
@@ -10503,7 +10667,7 @@
         <v>21</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
@@ -10541,7 +10705,7 @@
         <v>24</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
@@ -10579,7 +10743,7 @@
         <v>26</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
@@ -10617,7 +10781,7 @@
         <v>28</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
@@ -10655,10 +10819,10 @@
         <v>30</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
@@ -10696,7 +10860,7 @@
         <v>32</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
@@ -10734,7 +10898,7 @@
         <v>34</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
@@ -10772,7 +10936,7 @@
         <v>36</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.35">
@@ -10810,7 +10974,7 @@
         <v>38</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.35">
@@ -10848,7 +11012,7 @@
         <v>40</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.35">
@@ -10886,7 +11050,7 @@
         <v>42</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="17" spans="1:16" x14ac:dyDescent="0.35">
@@ -10924,7 +11088,7 @@
         <v>44</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="18" spans="1:16" x14ac:dyDescent="0.35">
@@ -10962,7 +11126,7 @@
         <v>46</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="19" spans="1:16" x14ac:dyDescent="0.35">
@@ -11000,7 +11164,7 @@
         <v>49</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="20" spans="1:16" x14ac:dyDescent="0.35">
@@ -11038,7 +11202,7 @@
         <v>51</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="21" spans="1:16" x14ac:dyDescent="0.35">
@@ -11073,7 +11237,7 @@
         <v>4</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="22" spans="1:16" x14ac:dyDescent="0.35">
@@ -11111,7 +11275,7 @@
         <v>53</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:16" x14ac:dyDescent="0.35">
@@ -11146,10 +11310,10 @@
         <v>1</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:16" x14ac:dyDescent="0.35">
@@ -11184,10 +11348,10 @@
         <v>4</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="25" spans="1:16" x14ac:dyDescent="0.35">
@@ -11222,7 +11386,7 @@
         <v>3</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="26" spans="1:16" x14ac:dyDescent="0.35">
@@ -11257,13 +11421,13 @@
         <v>4</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:16" x14ac:dyDescent="0.35">
@@ -11298,7 +11462,7 @@
         <v>3</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="28" spans="1:16" x14ac:dyDescent="0.35">
@@ -11333,10 +11497,10 @@
         <v>2</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="29" spans="1:16" x14ac:dyDescent="0.35">
@@ -11371,10 +11535,10 @@
         <v>3</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="30" spans="1:16" x14ac:dyDescent="0.35">
@@ -11409,10 +11573,10 @@
         <v>3</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="31" spans="1:16" x14ac:dyDescent="0.35">
@@ -11432,7 +11596,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="G31" s="1">
         <v>2</v>
@@ -11450,10 +11614,10 @@
         <v>4</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:16" x14ac:dyDescent="0.35">
@@ -11488,10 +11652,10 @@
         <v>4</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.35">
@@ -11526,10 +11690,10 @@
         <v>4</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="34" spans="1:16" x14ac:dyDescent="0.35">
@@ -11564,7 +11728,7 @@
         <v>3</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="35" spans="1:16" x14ac:dyDescent="0.35">
@@ -11599,7 +11763,7 @@
         <v>4</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="36" spans="1:16" x14ac:dyDescent="0.35">
@@ -11634,10 +11798,10 @@
         <v>4</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="37" spans="1:16" x14ac:dyDescent="0.35">
@@ -11672,10 +11836,10 @@
         <v>4</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="38" spans="1:16" x14ac:dyDescent="0.35">
@@ -11710,13 +11874,13 @@
         <v>2</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="39" spans="1:16" x14ac:dyDescent="0.35">
@@ -11751,10 +11915,10 @@
         <v>4</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="40" spans="1:16" x14ac:dyDescent="0.35">
@@ -11789,10 +11953,10 @@
         <v>4</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="41" spans="1:16" x14ac:dyDescent="0.35">
@@ -11827,7 +11991,7 @@
         <v>4</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="42" spans="1:16" x14ac:dyDescent="0.35">
@@ -11862,10 +12026,10 @@
         <v>3</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" spans="1:16" x14ac:dyDescent="0.35">
@@ -11900,7 +12064,7 @@
         <v>3</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="44" spans="1:16" x14ac:dyDescent="0.35">
@@ -11935,10 +12099,10 @@
         <v>4</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="45" spans="1:16" x14ac:dyDescent="0.35">
@@ -11973,10 +12137,10 @@
         <v>4</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.35">
@@ -12011,10 +12175,10 @@
         <v>4</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="47" spans="1:16" x14ac:dyDescent="0.35">
@@ -12049,10 +12213,10 @@
         <v>4</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="48" spans="1:16" x14ac:dyDescent="0.35">
@@ -12087,7 +12251,7 @@
         <v>4</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="49" spans="1:16" x14ac:dyDescent="0.35">
@@ -12107,7 +12271,7 @@
         <v>1</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G49" s="1">
         <v>2</v>
@@ -12125,7 +12289,7 @@
         <v>2</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="50" spans="1:16" x14ac:dyDescent="0.35">
@@ -12160,10 +12324,10 @@
         <v>4</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.35">
@@ -12183,7 +12347,7 @@
         <v>1</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="G51" s="1">
         <v>2</v>
@@ -12201,7 +12365,7 @@
         <v>2</v>
       </c>
       <c r="P51" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="52" spans="1:16" x14ac:dyDescent="0.35">
@@ -12236,13 +12400,13 @@
         <v>3</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="53" spans="1:16" x14ac:dyDescent="0.35">
@@ -12277,10 +12441,10 @@
         <v>4</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="54" spans="1:16" x14ac:dyDescent="0.35">
@@ -12315,10 +12479,10 @@
         <v>3</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.35">
@@ -12338,7 +12502,7 @@
         <v>1</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G55" s="1">
         <v>2</v>
@@ -12356,10 +12520,10 @@
         <v>3</v>
       </c>
       <c r="L55" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.35">
@@ -12394,10 +12558,10 @@
         <v>4</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="57" spans="1:16" x14ac:dyDescent="0.35">
@@ -12432,10 +12596,10 @@
         <v>3</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="58" spans="1:16" x14ac:dyDescent="0.35">
@@ -12470,7 +12634,7 @@
         <v>4</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="59" spans="1:16" x14ac:dyDescent="0.35">
@@ -12505,7 +12669,7 @@
         <v>4</v>
       </c>
       <c r="P59" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.35">
@@ -12540,7 +12704,7 @@
         <v>4</v>
       </c>
       <c r="P60" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="61" spans="1:16" x14ac:dyDescent="0.35">
@@ -12575,10 +12739,10 @@
         <v>3</v>
       </c>
       <c r="L61" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="P61" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="62" spans="1:16" x14ac:dyDescent="0.35">
@@ -12613,10 +12777,10 @@
         <v>4</v>
       </c>
       <c r="L62" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="M62" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:16" x14ac:dyDescent="0.35">
@@ -12651,10 +12815,10 @@
         <v>3</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="64" spans="1:16" x14ac:dyDescent="0.35">
@@ -12689,10 +12853,10 @@
         <v>2</v>
       </c>
       <c r="L64" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="M64" s="1" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="65" spans="1:16" x14ac:dyDescent="0.35">
@@ -12727,7 +12891,7 @@
         <v>4</v>
       </c>
       <c r="P65" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="66" spans="1:16" x14ac:dyDescent="0.35">
@@ -12747,7 +12911,7 @@
         <v>1</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G66" s="1">
         <v>1</v>
@@ -12765,10 +12929,10 @@
         <v>1</v>
       </c>
       <c r="L66" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="P66" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:16" x14ac:dyDescent="0.35">
@@ -12803,10 +12967,10 @@
         <v>3</v>
       </c>
       <c r="L67" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="P67" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="68" spans="1:16" x14ac:dyDescent="0.35">
@@ -12841,10 +13005,10 @@
         <v>2</v>
       </c>
       <c r="L68" s="1" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="P68" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="69" spans="1:16" x14ac:dyDescent="0.35">
@@ -12879,10 +13043,10 @@
         <v>2</v>
       </c>
       <c r="L69" s="1" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="P69" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="70" spans="1:16" x14ac:dyDescent="0.35">
@@ -12917,7 +13081,7 @@
         <v>3</v>
       </c>
       <c r="P70" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="71" spans="1:16" x14ac:dyDescent="0.35">
@@ -12937,7 +13101,7 @@
         <v>1</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G71" s="1">
         <v>2</v>
@@ -12955,7 +13119,7 @@
         <v>4</v>
       </c>
       <c r="P71" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="72" spans="1:16" x14ac:dyDescent="0.35">
@@ -12990,10 +13154,10 @@
         <v>4</v>
       </c>
       <c r="L72" s="1" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="P72" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
     <row r="73" spans="1:16" x14ac:dyDescent="0.35">
@@ -13028,10 +13192,10 @@
         <v>3</v>
       </c>
       <c r="L73" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="P73" s="1" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -13053,111 +13217,153 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63338982-E92B-4E40-B804-76232AB6A0F1}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:P5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.36328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="24.54296875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="32.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="24.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="B1" t="s">
+        <v>150</v>
+      </c>
+      <c r="C1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E1" t="s">
         <v>153</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>154</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
+        <v>207</v>
+      </c>
+      <c r="H1" t="s">
+        <v>208</v>
+      </c>
+      <c r="I1" t="s">
+        <v>209</v>
+      </c>
+      <c r="J1" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>147</v>
+      </c>
+      <c r="B2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F2" t="s">
+        <v>197</v>
+      </c>
+      <c r="G2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H2" t="s">
+        <v>199</v>
+      </c>
+      <c r="I2" t="s">
+        <v>200</v>
+      </c>
+      <c r="J2" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2" t="s">
+        <v>202</v>
+      </c>
+      <c r="L2" t="s">
+        <v>203</v>
+      </c>
+      <c r="M2" t="s">
+        <v>204</v>
+      </c>
+      <c r="N2" t="s">
+        <v>221</v>
+      </c>
+      <c r="O2" t="s">
+        <v>205</v>
+      </c>
+      <c r="P2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" t="s">
         <v>155</v>
       </c>
-      <c r="E1" t="s">
+      <c r="C3" t="s">
         <v>156</v>
       </c>
-      <c r="F1" t="s">
+      <c r="D3" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C2" t="s">
-        <v>184</v>
-      </c>
-      <c r="D2" t="s">
-        <v>55</v>
-      </c>
-      <c r="E2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>151</v>
-      </c>
-      <c r="B3" t="s">
-        <v>158</v>
-      </c>
-      <c r="C3" t="s">
-        <v>159</v>
-      </c>
-      <c r="D3" t="s">
-        <v>160</v>
-      </c>
       <c r="E3" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="F3" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C4" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D4" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="E4" t="s">
         <v>47</v>
       </c>
       <c r="F4" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="C5" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D5" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="E5" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
